--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,10 +40,25 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>firstname last name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+    <x:t>test potential client xLHnW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>142</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">test </x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC staus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -107,8 +122,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G2" totalsRowShown="0">
-  <x:autoFilter ref="A1:G2"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G3" totalsRowShown="0">
+  <x:autoFilter ref="A1:G3"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -410,7 +425,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G2"/>
+  <x:dimension ref="A1:G3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -443,8 +458,28 @@
       <x:c r="B2" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client xLHnW</x:t>
+    <x:t>test potential client X7Bcy</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -50,6 +50,12 @@
   </x:si>
   <x:si>
     <x:t>142</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">karshia </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz1@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">test </x:t>
@@ -122,8 +128,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G3" totalsRowShown="0">
-  <x:autoFilter ref="A1:G3"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G4" totalsRowShown="0">
+  <x:autoFilter ref="A1:G4"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -425,7 +431,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G3"/>
+  <x:dimension ref="A1:G4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -475,11 +481,22 @@
       <x:c r="B3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>14</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client X7Bcy</x:t>
+    <x:t>test potential client Khfub</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client Khfub</x:t>
+    <x:t>test potential client HIrKY</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,19 +52,10 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">karshia </x:t>
+    <x:t>mil test</x:t>
   </x:si>
   <x:si>
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">test </x:t>
-  </x:si>
-  <x:si>
-    <x:t>QC staus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -128,8 +119,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G4" totalsRowShown="0">
-  <x:autoFilter ref="A1:G4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G3" totalsRowShown="0">
+  <x:autoFilter ref="A1:G3"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -431,7 +422,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G4"/>
+  <x:dimension ref="A1:G3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -483,20 +474,6 @@
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client HIrKY</x:t>
+    <x:t>test potential client utbjj</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client utbjj</x:t>
+    <x:t>test potential client wNnVA</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -50,6 +50,9 @@
   </x:si>
   <x:si>
     <x:t>142</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">test </x:t>
   </x:si>
   <x:si>
     <x:t>mil test</x:t>
@@ -119,8 +122,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G3" totalsRowShown="0">
-  <x:autoFilter ref="A1:G3"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G4" totalsRowShown="0">
+  <x:autoFilter ref="A1:G4"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -422,7 +425,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G3"/>
+  <x:dimension ref="A1:G4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -472,8 +475,16 @@
       <x:c r="B3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client wNnVA</x:t>
+    <x:t>test potential client X3Hlh</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client X3Hlh</x:t>
+    <x:t>test potential client 9QzY7</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client 9QzY7</x:t>
+    <x:t>test potential client 7lZNn</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,7 +52,31 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">test </x:t>
+    <x:t xml:space="preserve">branch </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>clie t</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/29/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34324324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consultation</x:t>
   </x:si>
   <x:si>
     <x:t>mil test</x:t>
@@ -122,8 +146,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G4" totalsRowShown="0">
-  <x:autoFilter ref="A1:G4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G8" totalsRowShown="0">
+  <x:autoFilter ref="A1:G8"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -425,7 +449,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G4"/>
+  <x:dimension ref="A1:G8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -483,8 +507,49 @@
       <x:c r="B4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client 7lZNn</x:t>
+    <x:t>test potential client i5NSP</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -50,6 +50,9 @@
   </x:si>
   <x:si>
     <x:t>142</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">potential </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">branch </x:t>
@@ -146,8 +149,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G8" totalsRowShown="0">
-  <x:autoFilter ref="A1:G8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G9" totalsRowShown="0">
+  <x:autoFilter ref="A1:G9"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -449,7 +452,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G8"/>
+  <x:dimension ref="A1:G9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -526,30 +529,38 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
+    </x:row>
+    <x:row r="9" spans="1:7">
+      <x:c r="A9" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>22</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client i5NSP</x:t>
+    <x:t>test potential client 8XIBL</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,7 +52,10 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">potential </x:t>
+    <x:t>potential test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC staus</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">branch </x:t>
@@ -64,7 +67,7 @@
     <x:t>nabeel ahmed</x:t>
   </x:si>
   <x:si>
-    <x:t>clie t</x:t>
+    <x:t>clie tim</x:t>
   </x:si>
   <x:si>
     <x:t>03/29/2023 00:00:00 +00:00</x:t>
@@ -502,13 +505,16 @@
       <x:c r="B3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
@@ -516,7 +522,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -524,7 +530,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -532,24 +538,24 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -557,10 +563,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client 8XIBL</x:t>
+    <x:t>test potential client Fdnpv</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,16 +52,58 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
+    <x:t>05/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test qhem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44444444444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appeal - IPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/09/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>add potential client test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332323232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC staus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>canada visa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>automation custom</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bbbbbbbbbbbbbbbb </x:t>
+  </x:si>
+  <x:si>
+    <x:t>branch manager</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmd</x:t>
+  </x:si>
+  <x:si>
     <x:t>potential test</x:t>
   </x:si>
   <x:si>
-    <x:t>QC staus</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">branch </x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmd</x:t>
   </x:si>
   <x:si>
     <x:t>nabeel ahmed</x:t>
@@ -152,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G9" totalsRowShown="0">
-  <x:autoFilter ref="A1:G9"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G16" totalsRowShown="0">
+  <x:autoFilter ref="A1:G16"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -455,7 +497,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G9"/>
+  <x:dimension ref="A1:G16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -500,21 +542,42 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
@@ -522,7 +585,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -530,7 +593,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -538,24 +601,15 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -563,10 +617,78 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
+      <x:c r="A10" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
+      <x:c r="A11" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:7">
+      <x:c r="A12" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:7">
+      <x:c r="A13" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:7">
+      <x:c r="A14" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:7">
+      <x:c r="A15" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:7">
+      <x:c r="A16" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client Fdnpv</x:t>
+    <x:t>test potential client vkgbt</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,6 +52,18 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
+    <x:t>05/24/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmi gandazia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3232323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC staus</x:t>
+  </x:si>
+  <x:si>
     <x:t>05/15/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
@@ -74,9 +86,6 @@
   </x:si>
   <x:si>
     <x:t>332323232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QC staus</x:t>
   </x:si>
   <x:si>
     <x:t>test123@gmail.com</x:t>
@@ -194,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G16" totalsRowShown="0">
-  <x:autoFilter ref="A1:G16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G17" totalsRowShown="0">
+  <x:autoFilter ref="A1:G17"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -497,7 +506,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G16"/>
+  <x:dimension ref="A1:G17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -550,42 +559,48 @@
       <x:c r="C3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="D3" s="0" t="s">
         <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="C4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="F4" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -593,7 +608,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -601,7 +616,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
@@ -609,7 +624,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -625,10 +640,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
@@ -636,7 +648,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
@@ -644,7 +659,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
@@ -660,35 +675,43 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>38</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:7">
+      <x:c r="A17" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client vkgbt</x:t>
+    <x:t>test potential client e5WTD</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,42 +52,99 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
-    <x:t>05/24/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>carmi gandazia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3232323</x:t>
+    <x:t xml:space="preserve">milan </x:t>
+  </x:si>
+  <x:si>
+    <x:t>puraniemailma@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maryem a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maryem@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">imran khan </x:t>
+  </x:si>
+  <x:si>
+    <x:t>imrankhan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mawaz ijaz </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nawazsharifchor@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nz immi GRANT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nzimmigrationadvisor@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">test </x:t>
+  </x:si>
+  <x:si>
+    <x:t>testnabeel@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">cutus </x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel@outsourcenz.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>preshan hona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>preshan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel 1 ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>949944</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test0@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test qhem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44444444444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appeal - IPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/09/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>add potential client test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332323232</x:t>
   </x:si>
   <x:si>
     <x:t>QC staus</x:t>
   </x:si>
   <x:si>
-    <x:t>05/15/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test qhem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44444444444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appeal - IPT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/09/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>add potential client test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>332323232</x:t>
-  </x:si>
-  <x:si>
     <x:t>test123@gmail.com</x:t>
   </x:si>
   <x:si>
@@ -97,15 +154,15 @@
     <x:t>2</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">bbbbbbbbbbbbbbbb </x:t>
+  </x:si>
+  <x:si>
+    <x:t>branch manager</x:t>
+  </x:si>
+  <x:si>
     <x:t>automation custom</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">bbbbbbbbbbbbbbbb </x:t>
-  </x:si>
-  <x:si>
-    <x:t>branch manager</x:t>
-  </x:si>
-  <x:si>
     <x:t>nabeel ahmd</x:t>
   </x:si>
   <x:si>
@@ -113,9 +170,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">branch </x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel ahmed</x:t>
   </x:si>
   <x:si>
     <x:t>clie tim</x:t>
@@ -203,8 +257,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G17" totalsRowShown="0">
-  <x:autoFilter ref="A1:G17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G25" totalsRowShown="0">
+  <x:autoFilter ref="A1:G25"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
@@ -506,7 +560,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G17"/>
+  <x:dimension ref="A1:G25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -551,56 +605,35 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -608,7 +641,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -616,7 +652,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
@@ -624,7 +663,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -632,7 +674,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
@@ -640,7 +685,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
@@ -648,10 +696,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
@@ -661,21 +715,54 @@
       <x:c r="B12" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
@@ -683,24 +770,15 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
@@ -708,10 +786,86 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:7">
+      <x:c r="A18" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:7">
+      <x:c r="A19" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:7">
+      <x:c r="A20" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:7">
+      <x:c r="A21" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:7">
+      <x:c r="A22" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:7">
+      <x:c r="A23" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7">
+      <x:c r="A24" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7">
+      <x:c r="A25" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client nrLik</x:t>
+    <x:t>test potential client LjI6Q</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -40,7 +40,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client LjI6Q</x:t>
+    <x:t>test potential client f9bVI</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,21 +52,24 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
+    <x:t>Abcd Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcfh4@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125412</x:t>
+  </x:si>
+  <x:si>
     <x:t>nbaaa Efgh</x:t>
   </x:si>
   <x:si>
-    <x:t>0300000000000</x:t>
-  </x:si>
-  <x:si>
     <x:t>move to client</x:t>
   </x:si>
   <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>125412</x:t>
-  </x:si>
-  <x:si>
     <x:t>abcd34324@mail.com</x:t>
   </x:si>
   <x:si>
@@ -152,9 +155,6 @@
   </x:si>
   <x:si>
     <x:t>ninetag@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Abcd Efgh</x:t>
   </x:si>
   <x:si>
     <x:t>abcd@mail.com</x:t>
@@ -766,14 +766,11 @@
       <x:c r="C3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
@@ -781,19 +778,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
@@ -801,19 +798,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -821,19 +818,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -841,19 +838,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
@@ -861,19 +858,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -881,19 +878,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
@@ -901,16 +898,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
@@ -918,16 +915,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
@@ -935,16 +932,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
@@ -952,16 +949,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
@@ -969,16 +966,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
@@ -986,16 +983,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
@@ -1003,16 +1000,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
@@ -1020,16 +1017,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
@@ -1037,16 +1034,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
@@ -1054,16 +1051,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -1071,19 +1068,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
@@ -1091,10 +1088,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
@@ -1102,7 +1099,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>13</x:v>
@@ -1111,7 +1108,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
@@ -1122,7 +1119,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
@@ -1363,7 +1360,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
         <x:v>94</x:v>
@@ -1415,7 +1412,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -37,10 +37,13 @@
     <x:t>Worth</x:t>
   </x:si>
   <x:si>
+    <x:t>Processing Persons</x:t>
+  </x:si>
+  <x:si>
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client f9bVI</x:t>
+    <x:t>test potential client LoqCD</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -52,6 +55,9 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>Abcd Efgh</x:t>
   </x:si>
   <x:si>
@@ -64,6 +70,9 @@
     <x:t>125412</x:t>
   </x:si>
   <x:si>
+    <x:t>exteme team</x:t>
+  </x:si>
+  <x:si>
     <x:t>nbaaa Efgh</x:t>
   </x:si>
   <x:si>
@@ -157,6 +166,9 @@
     <x:t>ninetag@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel, team member nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>abcd@mail.com</x:t>
   </x:si>
   <x:si>
@@ -307,6 +319,9 @@
     <x:t>2</x:t>
   </x:si>
   <x:si>
+    <x:t>arsalan team member, Owner nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">bbbbbbbbbbbbbbbb </x:t>
   </x:si>
   <x:si>
@@ -322,12 +337,18 @@
     <x:t>potential test</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, exteme team, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, arsalan team member</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">branch </x:t>
   </x:si>
   <x:si>
     <x:t>clie tim</x:t>
   </x:si>
   <x:si>
+    <x:t>arsalan team member, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, team member nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>03/29/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
@@ -347,6 +368,9 @@
   </x:si>
   <x:si>
     <x:t>nabeeloutsourcenz1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel, arsalan team member, Nabeel Ahmed, Nabeel Ahmed</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -410,9 +434,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:G54" totalsRowShown="0">
-  <x:autoFilter ref="A1:G54"/>
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:H54" totalsRowShown="0">
+  <x:autoFilter ref="A1:H54"/>
+  <x:tableColumns count="8">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="Full Name"/>
     <x:tableColumn id="3" name="Mobile"/>
@@ -420,6 +444,7 @@
     <x:tableColumn id="5" name="Email"/>
     <x:tableColumn id="6" name="Intrested Visa"/>
     <x:tableColumn id="7" name="Worth"/>
+    <x:tableColumn id="8" name="Processing Persons"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -713,10 +738,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G54"/>
+  <x:dimension ref="A1:H54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:8">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -738,741 +763,864 @@
       <x:c r="G1" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8">
       <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="A7" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8">
+      <x:c r="A8" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8">
+      <x:c r="A9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
+      <x:c r="A10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8">
+      <x:c r="A11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8">
+      <x:c r="A12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8">
+      <x:c r="A13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:8">
+      <x:c r="A14" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:8">
+      <x:c r="A15" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:8">
+      <x:c r="A16" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:8">
+      <x:c r="A17" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:8">
+      <x:c r="A18" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:8">
+      <x:c r="A19" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:8">
+      <x:c r="A20" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:8">
+      <x:c r="A21" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:8">
+      <x:c r="A22" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="C22" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:8">
+      <x:c r="A23" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:8">
+      <x:c r="A24" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:8">
+      <x:c r="A25" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:8">
+      <x:c r="A26" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:8">
+      <x:c r="A27" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:8">
+      <x:c r="A28" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:8">
+      <x:c r="A29" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:8">
+      <x:c r="A30" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:8">
+      <x:c r="A31" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:8">
+      <x:c r="A32" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:8">
+      <x:c r="A33" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:8">
+      <x:c r="A34" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:8">
+      <x:c r="A35" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:8">
+      <x:c r="A36" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:8">
+      <x:c r="A37" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:8">
+      <x:c r="A38" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:8">
+      <x:c r="A39" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:8">
+      <x:c r="A40" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:8">
+      <x:c r="A41" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:8">
+      <x:c r="A42" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:8">
+      <x:c r="A43" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:8">
+      <x:c r="A44" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
+    </x:row>
+    <x:row r="45" spans="1:8">
+      <x:c r="A45" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:8">
+      <x:c r="A46" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:8">
+      <x:c r="A47" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:8">
+      <x:c r="A48" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
-      <x:c r="A9" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
-      <x:c r="A12" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
-      <x:c r="A13" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:7">
-      <x:c r="A14" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:7">
-      <x:c r="A15" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:7">
-      <x:c r="A16" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:7">
-      <x:c r="A17" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:7">
-      <x:c r="A18" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:7">
-      <x:c r="A19" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:7">
-      <x:c r="A20" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:7">
-      <x:c r="A21" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:7">
-      <x:c r="A22" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:7">
-      <x:c r="A23" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E23" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:7">
-      <x:c r="A24" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:7">
-      <x:c r="A25" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:7">
-      <x:c r="A26" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:7">
-      <x:c r="A27" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E27" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:7">
-      <x:c r="A28" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:7">
-      <x:c r="A29" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:7">
-      <x:c r="A30" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:7">
-      <x:c r="A31" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:7">
-      <x:c r="A32" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E32" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:7">
-      <x:c r="A33" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E33" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:7">
-      <x:c r="A34" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E34" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:7">
-      <x:c r="A35" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:7">
-      <x:c r="A36" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E36" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:7">
-      <x:c r="A37" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:7">
-      <x:c r="A38" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:7">
-      <x:c r="A39" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:7">
-      <x:c r="A40" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:7">
-      <x:c r="A41" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:7">
-      <x:c r="A42" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
+      <x:c r="H48" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:8">
+      <x:c r="A49" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:8">
+      <x:c r="A50" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:8">
+      <x:c r="A51" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:7">
-      <x:c r="A43" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:7">
-      <x:c r="A44" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:7">
-      <x:c r="A45" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:7">
-      <x:c r="A46" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:7">
-      <x:c r="A47" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:7">
-      <x:c r="A48" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:7">
-      <x:c r="A49" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:7">
-      <x:c r="A50" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:7">
-      <x:c r="A51" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:7">
+    </x:row>
+    <x:row r="52" spans="1:8">
       <x:c r="A52" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:7">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:8">
       <x:c r="A53" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:7">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:8">
       <x:c r="A54" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>118</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -43,7 +43,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client LoqCD</x:t>
+    <x:t>test potential client ev431</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -43,7 +43,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client ev431</x:t>
+    <x:t>test potential client w1KVX</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -43,7 +43,7 @@
     <x:t>01/01/1900 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>test potential client w1KVX</x:t>
+    <x:t>test potential client K5AKK</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>CKKYN</x:t>
+    <x:t>XuqHM</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>XuqHM</x:t>
+    <x:t>dOZL8</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>dOZL8</x:t>
+    <x:t>Ge2ut</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -85,21 +85,15 @@
     <x:t>exteme team</x:t>
   </x:si>
   <x:si>
-    <x:t>nbaaa</x:t>
+    <x:t>mawaz102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
   </x:si>
   <x:si>
     <x:t>move to client</x:t>
   </x:si>
   <x:si>
-    <x:t>abcd34324@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
     <x:t>mawaz6949@mail.com</x:t>
   </x:si>
   <x:si>
@@ -277,9 +271,6 @@
     <x:t>GRANT</x:t>
   </x:si>
   <x:si>
-    <x:t>testnabeel@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>cutus</x:t>
   </x:si>
   <x:si>
@@ -368,12 +359,6 @@
   </x:si>
   <x:si>
     <x:t>ahmd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>potential</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, exteme team, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Owner nabeel, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, arsalan team member</x:t>
   </x:si>
   <x:si>
     <x:t>clie</x:t>
@@ -470,8 +455,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J54" totalsRowShown="0">
-  <x:autoFilter ref="A1:J54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J51" totalsRowShown="0">
+  <x:autoFilter ref="A1:J51"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="First Name"/>
@@ -776,7 +761,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J54"/>
+  <x:dimension ref="A1:J51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -865,22 +850,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10">
@@ -888,68 +873,68 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>21</x:v>
@@ -963,19 +948,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>21</x:v>
@@ -989,17 +974,14 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -1018,7 +1000,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>19</x:v>
@@ -1041,7 +1023,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>19</x:v>
@@ -1064,7 +1046,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>19</x:v>
@@ -1087,7 +1069,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>19</x:v>
@@ -1107,16 +1089,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
         <x:v>21</x:v>
@@ -1130,16 +1112,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
         <x:v>21</x:v>
@@ -1153,16 +1135,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>21</x:v>
@@ -1176,16 +1158,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>21</x:v>
@@ -1199,10 +1181,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>19</x:v>
@@ -1222,16 +1204,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>21</x:v>
@@ -1245,25 +1230,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1271,13 +1244,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
@@ -1285,19 +1267,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I22" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>16</x:v>
@@ -1308,10 +1281,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>16</x:v>
@@ -1394,8 +1367,11 @@
       <x:c r="B29" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
         <x:v>16</x:v>
@@ -1406,9 +1382,6 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
@@ -1439,8 +1412,11 @@
       <x:c r="B32" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
         <x:v>16</x:v>
@@ -1451,9 +1427,6 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
@@ -1484,8 +1457,11 @@
       <x:c r="B35" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
         <x:v>16</x:v>
@@ -1498,14 +1474,8 @@
       <x:c r="B36" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D36" s="0" t="s">
+      <x:c r="G36" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="G36" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="J36" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:10">
@@ -1513,10 +1483,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
@@ -1524,10 +1497,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
@@ -1535,101 +1517,89 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="I40" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
       <x:c r="A42" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E42" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G42" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H42" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
       <x:c r="A43" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H43" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="I43" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="J43" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
     </x:row>
@@ -1640,8 +1610,8 @@
       <x:c r="B44" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="J44" s="0" t="s">
-        <x:v>22</x:v>
+      <x:c r="D44" s="0" t="s">
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
@@ -1649,7 +1619,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>114</x:v>
@@ -1660,10 +1630,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
@@ -1671,10 +1638,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
@@ -1682,16 +1649,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J48" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
@@ -1699,18 +1660,36 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:10">
@@ -1718,64 +1697,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:10">
-      <x:c r="A52" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D52" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="J52" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:10">
-      <x:c r="A53" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
+      <x:c r="J51" s="0" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="G53" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H53" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="J53" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:10">
-      <x:c r="A54" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G54" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="J54" s="0" t="s">
-        <x:v>130</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>Ge2ut</x:t>
+    <x:t>6GzED</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>6GzED</x:t>
+    <x:t>yLzXz</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -67,6 +67,9 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
+    <x:t>jan</x:t>
+  </x:si>
+  <x:si>
     <x:t>Abcd</x:t>
   </x:si>
   <x:si>
@@ -76,46 +79,34 @@
     <x:t>0300000000000</x:t>
   </x:si>
   <x:si>
-    <x:t>abcfh4@gmail.com</x:t>
-  </x:si>
-  <x:si>
     <x:t>125412</x:t>
   </x:si>
   <x:si>
     <x:t>exteme team</x:t>
   </x:si>
   <x:si>
-    <x:t>mawaz102</x:t>
+    <x:t>mawaz101</x:t>
   </x:si>
   <x:si>
     <x:t>test</x:t>
   </x:si>
   <x:si>
+    <x:t>QC staus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6970@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rahlyayaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raa22344erf1@gmail.com</x:t>
+  </x:si>
+  <x:si>
     <x:t>move to client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6949@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QC staus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6970@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rahlyayaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raa22344erf1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raa223441@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>raamamama3441@gmail.com</x:t>
@@ -455,8 +446,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J51" totalsRowShown="0">
-  <x:autoFilter ref="A1:J51"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J50" totalsRowShown="0">
+  <x:autoFilter ref="A1:J50"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="First Name"/>
@@ -761,7 +752,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J51"/>
+  <x:dimension ref="A1:J50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -826,20 +817,8 @@
       <x:c r="B3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
@@ -847,19 +826,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>21</x:v>
@@ -873,19 +846,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>21</x:v>
@@ -896,19 +869,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>21</x:v>
@@ -922,19 +895,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="G7" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>21</x:v>
@@ -948,19 +921,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>21</x:v>
@@ -974,16 +944,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
         <x:v>21</x:v>
@@ -997,16 +967,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>21</x:v>
@@ -1020,16 +990,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>21</x:v>
@@ -1043,16 +1013,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>21</x:v>
@@ -1066,16 +1036,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>21</x:v>
@@ -1089,16 +1059,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
         <x:v>21</x:v>
@@ -1112,16 +1082,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
         <x:v>21</x:v>
@@ -1135,16 +1105,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>21</x:v>
@@ -1158,16 +1128,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
         <x:v>21</x:v>
@@ -1181,16 +1151,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>21</x:v>
@@ -1206,23 +1179,11 @@
       <x:c r="B19" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="G19" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="I19" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
@@ -1230,13 +1191,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>53</x:v>
+      <x:c r="I20" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1244,19 +1214,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>16</x:v>
@@ -1267,10 +1228,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>16</x:v>
@@ -1281,10 +1242,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>16</x:v>
@@ -1295,10 +1256,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
         <x:v>16</x:v>
@@ -1309,10 +1270,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>16</x:v>
@@ -1323,10 +1284,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
         <x:v>16</x:v>
@@ -1337,10 +1298,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
         <x:v>16</x:v>
@@ -1351,6 +1312,9 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
@@ -1367,11 +1331,8 @@
       <x:c r="B29" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D29" s="0" t="s">
+      <x:c r="G29" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
         <x:v>16</x:v>
@@ -1382,10 +1343,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
         <x:v>16</x:v>
@@ -1396,6 +1357,9 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
@@ -1412,11 +1376,8 @@
       <x:c r="B32" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D32" s="0" t="s">
+      <x:c r="G32" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
         <x:v>16</x:v>
@@ -1427,10 +1388,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
         <x:v>16</x:v>
@@ -1441,10 +1402,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
         <x:v>16</x:v>
@@ -1455,16 +1419,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J35" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10">
@@ -1472,6 +1430,9 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
@@ -1488,8 +1449,14 @@
       <x:c r="D37" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10">
@@ -1497,88 +1464,79 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10">
       <x:c r="A39" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="I39" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10">
       <x:c r="A40" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J40" s="0" t="s">
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:10">
       <x:c r="A41" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:10">
@@ -1586,10 +1544,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="J42" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:10">
@@ -1597,10 +1555,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:10">
@@ -1608,10 +1566,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:10">
@@ -1619,10 +1577,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:10">
@@ -1630,7 +1585,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:10">
@@ -1638,10 +1596,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:10">
@@ -1649,64 +1607,53 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:10">
       <x:c r="A49" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:10">
       <x:c r="A50" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="H50" s="0" t="s">
+      <x:c r="J50" s="0" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="J50" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:10">
-      <x:c r="A51" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G51" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="J51" s="0" t="s">
-        <x:v>125</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -46,13 +46,13 @@
     <x:t>Processing Persons</x:t>
   </x:si>
   <x:si>
-    <x:t>01/01/1900 00:00:00 +00:00</x:t>
+    <x:t>EZMId</x:t>
   </x:si>
   <x:si>
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>yLzXz</x:t>
+    <x:t>o2Axz</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -67,7 +67,7 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>jan</x:t>
+    <x:t>PC-B517-DVQ1</x:t>
   </x:si>
   <x:si>
     <x:t>Abcd</x:t>
@@ -79,264 +79,261 @@
     <x:t>0300000000000</x:t>
   </x:si>
   <x:si>
+    <x:t>move to client</x:t>
+  </x:si>
+  <x:si>
     <x:t>125412</x:t>
   </x:si>
   <x:si>
+    <x:t>exteme team, team member nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC staus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6970@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rahlyayaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raa22344erf1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama3441@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6984@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6987@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6983@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6981@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6982@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama344@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeee123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeelahmed23ee123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabila</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd123124@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd1234@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gr5545</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ninetag@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel, team member nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bhola driver</x:t>
+  </x:si>
+  <x:si>
+    <x:t>driverbhola@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dubai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dubaishrjah@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>influence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>influence@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tag10@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lomdon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>london@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nzimmigrationadvisor@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>eminem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>emp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>america123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>palestine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>palestine@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>milan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>puraniemailma@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maryem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maryem@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>imran khan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>imrankhan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz ijaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nawazsharifchor@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nz immi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRANT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cutus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel@outsourcenz.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>preshan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>preshan@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>949944</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test0@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>qhem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44444444444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed772@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appeal - IPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>add potential client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332323232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>canada visa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member, Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bbbbbbbbbbbbbbbb</x:t>
+  </x:si>
+  <x:si>
     <x:t>exteme team</x:t>
   </x:si>
   <x:si>
-    <x:t>mawaz101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QC staus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6970@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rahlyayaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raa22344erf1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>move to client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama3441@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6984@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6987@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6983@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6981@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6982@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama344@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeee123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeelahmed23ee123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabila</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abcd123124@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abcd1234@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gr5545</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ninetag@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel, team member nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abcd@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bhola driver</x:t>
-  </x:si>
-  <x:si>
-    <x:t>driverbhola@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dubai</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dubaishrjah@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>influence</x:t>
-  </x:si>
-  <x:si>
-    <x:t>influence@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tag10@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lomdon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>london@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nzimmigrationadvisor@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>eminem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>emp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>america123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>palestine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>palestine@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>milan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>puraniemailma@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maryem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>a</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maryem@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>imran khan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>imrankhan@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz ijaz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nawazsharifchor@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nz immi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRANT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cutus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel@outsourcenz.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>preshan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hona</x:t>
-  </x:si>
-  <x:si>
-    <x:t>preshan@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ahmed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>949944</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test0@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/15/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>qhem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44444444444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed772@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Appeal - IPT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/09/2023 00:00:00 +00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>add potential client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>332323232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>canada visa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member, Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bbbbbbbbbbbbbbbb</x:t>
-  </x:si>
-  <x:si>
     <x:t>branch</x:t>
   </x:si>
   <x:si>
@@ -359,9 +356,6 @@
   </x:si>
   <x:si>
     <x:t>arsalan team member, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, Nabeel Ahmed, team member nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/29/2023 00:00:00 +00:00</x:t>
   </x:si>
   <x:si>
     <x:t>nabel</x:t>
@@ -428,13 +422,20 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -446,9 +447,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:J50" totalsRowShown="0">
-  <x:autoFilter ref="A1:J50"/>
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K49" totalsRowShown="0">
+  <x:autoFilter ref="A1:K49"/>
+  <x:tableColumns count="11">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="First Name"/>
     <x:tableColumn id="3" name="Middle Name"/>
@@ -459,6 +460,7 @@
     <x:tableColumn id="8" name="Intrested Visa"/>
     <x:tableColumn id="9" name="Worth"/>
     <x:tableColumn id="10" name="Processing Persons"/>
+    <x:tableColumn id="11" name="EZMId"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -752,10 +754,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J50"/>
+  <x:dimension ref="A1:K49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:10">
+    <x:row r="1" spans="1:11">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -786,11 +788,11 @@
       <x:c r="J1" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:10">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="K1" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
       <x:c r="B2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -809,642 +811,552 @@
       <x:c r="J2" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:10">
-      <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11">
       <x:c r="B3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:10">
-      <x:c r="A4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:11">
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:10">
-      <x:c r="A5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="5" spans="1:11">
       <x:c r="B5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:10">
-      <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:11">
       <x:c r="B6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="B7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:10">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:10">
-      <x:c r="A8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="8" spans="1:11">
       <x:c r="B8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:10">
-      <x:c r="A9" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="9" spans="1:11">
       <x:c r="B9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:10">
-      <x:c r="A10" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="10" spans="1:11">
       <x:c r="B10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:10">
-      <x:c r="A11" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="11" spans="1:11">
       <x:c r="B11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:10">
-      <x:c r="A12" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="12" spans="1:11">
       <x:c r="B12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:10">
-      <x:c r="A13" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="13" spans="1:11">
       <x:c r="B13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:10">
-      <x:c r="A14" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="14" spans="1:11">
       <x:c r="B14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:10">
-      <x:c r="A15" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="15" spans="1:11">
       <x:c r="B15" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:10">
-      <x:c r="A16" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="16" spans="1:11">
       <x:c r="B16" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:10">
-      <x:c r="A17" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="17" spans="1:11">
       <x:c r="B17" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:10">
-      <x:c r="A18" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="18" spans="1:11">
       <x:c r="B18" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:11">
+      <x:c r="B19" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:10">
-      <x:c r="A19" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="G19" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:11">
+      <x:c r="B20" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:10">
-      <x:c r="A20" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I20" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:10">
-      <x:c r="A21" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="21" spans="1:11">
       <x:c r="B21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:10">
-      <x:c r="A22" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="22" spans="1:11">
       <x:c r="B22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:10">
-      <x:c r="A23" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="23" spans="1:11">
       <x:c r="B23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:10">
-      <x:c r="A24" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="24" spans="1:11">
       <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:10">
-      <x:c r="A25" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="25" spans="1:11">
       <x:c r="B25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:10">
-      <x:c r="A26" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="26" spans="1:11">
       <x:c r="B26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:10">
-      <x:c r="A27" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="27" spans="1:11">
       <x:c r="B27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:11">
+      <x:c r="B28" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:11">
+      <x:c r="B29" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:11">
+      <x:c r="B30" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:11">
+      <x:c r="B31" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:11">
+      <x:c r="B32" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:11">
+      <x:c r="B33" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="J27" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:10">
-      <x:c r="A28" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="J28" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:10">
-      <x:c r="A29" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="J29" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:10">
-      <x:c r="A30" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:10">
-      <x:c r="A31" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G31" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="J31" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:10">
-      <x:c r="A32" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:10">
-      <x:c r="A33" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="J33" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:10">
-      <x:c r="A34" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="34" spans="1:11">
       <x:c r="B34" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="J34" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:10">
-      <x:c r="A35" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:11">
       <x:c r="B35" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:10">
-      <x:c r="A36" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:11">
       <x:c r="B36" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:10">
-      <x:c r="A37" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:11">
       <x:c r="B37" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>88</x:v>
@@ -1453,207 +1365,160 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:10">
-      <x:c r="A38" s="0" t="s">
-        <x:v>10</x:v>
+    <x:row r="38" spans="1:11">
+      <x:c r="A38" s="1">
+        <x:v>45061</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="I38" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:10">
-      <x:c r="A39" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:11">
+      <x:c r="A39" s="1">
+        <x:v>45055</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:10">
-      <x:c r="A40" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:11">
       <x:c r="B40" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E40" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G40" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H40" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="I40" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:10">
-      <x:c r="A41" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="41" spans="1:11">
       <x:c r="B41" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="J41" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:10">
-      <x:c r="A42" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:11">
       <x:c r="B42" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:10">
-      <x:c r="A43" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:11">
       <x:c r="B43" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:10">
-      <x:c r="A44" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+    <x:row r="44" spans="1:11">
       <x:c r="B44" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:11">
+      <x:c r="B45" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:10">
-      <x:c r="A45" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:10">
-      <x:c r="A46" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:11">
       <x:c r="B46" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:11">
+      <x:c r="B47" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-    </x:row>
-    <x:row r="47" spans="1:10">
-      <x:c r="A47" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="D47" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:11">
+      <x:c r="A48" s="1">
+        <x:v>45014</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-    </x:row>
-    <x:row r="48" spans="1:10">
-      <x:c r="A48" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>113</x:v>
+      <x:c r="E48" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>117</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:10">
-      <x:c r="A49" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:11">
       <x:c r="B49" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H49" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:10">
-      <x:c r="A50" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G50" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="J50" s="0" t="s">
-        <x:v>122</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>o2Axz</x:t>
+    <x:t>qHaJ7</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -67,7 +67,100 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>PC-B517-DVQ1</x:t>
+    <x:t>PC-9F3D-XY42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC staus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125412</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rahlyayaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raa22344erf1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>move to client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama3441@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6984@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6987@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6983@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6981@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz6982@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama344@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeee123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeelahmed23ee123@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabila</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd123124@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abcd1234@mail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gr5545</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ninetag@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel, team member nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>Abcd</x:t>
@@ -76,102 +169,6 @@
     <x:t>Efgh</x:t>
   </x:si>
   <x:si>
-    <x:t>0300000000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>move to client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>125412</x:t>
-  </x:si>
-  <x:si>
-    <x:t>exteme team, team member nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QC staus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6970@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rahlyayaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raa22344erf1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama3441@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6984@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6987@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6983@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6981@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz6982@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama344@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeee123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeelahmed23ee123@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabila</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abcd123124@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abcd1234@mail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>gr5545</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ninetag@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel, team member nabeel</x:t>
-  </x:si>
-  <x:si>
     <x:t>abcd@mail.com</x:t>
   </x:si>
   <x:si>
@@ -227,6 +224,9 @@
   </x:si>
   <x:si>
     <x:t>palestine@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel, Nabeel Ahmed, team member nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>milan</x:t>
@@ -447,8 +447,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K49" totalsRowShown="0">
-  <x:autoFilter ref="A1:K49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K48" totalsRowShown="0">
+  <x:autoFilter ref="A1:K48"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="First Name"/>
@@ -754,7 +754,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K49"/>
+  <x:dimension ref="A1:K48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -828,11 +828,14 @@
       <x:c r="F3" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -846,33 +849,36 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="B5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
         <x:v>16</x:v>
@@ -880,22 +886,19 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="B6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
         <x:v>16</x:v>
@@ -903,19 +906,19 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="B7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>16</x:v>
@@ -923,19 +926,19 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="B8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>16</x:v>
@@ -943,19 +946,19 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="B9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
         <x:v>16</x:v>
@@ -963,19 +966,19 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="B10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>16</x:v>
@@ -983,7 +986,7 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="B11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>25</x:v>
@@ -992,10 +995,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
         <x:v>16</x:v>
@@ -1003,19 +1006,19 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="B12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
         <x:v>16</x:v>
@@ -1023,19 +1026,19 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="B13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
         <x:v>16</x:v>
@@ -1043,19 +1046,19 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="B14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
         <x:v>16</x:v>
@@ -1063,19 +1066,19 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="B15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
         <x:v>16</x:v>
@@ -1083,19 +1086,22 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="B16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
         <x:v>16</x:v>
@@ -1105,51 +1111,39 @@
       <x:c r="B17" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="G17" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="B18" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="B19" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
         <x:v>16</x:v>
@@ -1160,7 +1154,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>16</x:v>
@@ -1168,10 +1162,10 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="B21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>16</x:v>
@@ -1179,10 +1173,10 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="B22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>16</x:v>
@@ -1190,10 +1184,10 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="B23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>16</x:v>
@@ -1201,10 +1195,10 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="B24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
         <x:v>16</x:v>
@@ -1212,10 +1206,10 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="B25" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>16</x:v>
@@ -1223,10 +1217,13 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="B26" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
         <x:v>16</x:v>
@@ -1234,24 +1231,21 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="B27" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="B28" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
         <x:v>16</x:v>
@@ -1259,10 +1253,13 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="B29" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
         <x:v>16</x:v>
@@ -1270,13 +1267,10 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="B30" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
         <x:v>16</x:v>
@@ -1284,10 +1278,10 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="B31" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
         <x:v>16</x:v>
@@ -1295,10 +1289,13 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="B32" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
         <x:v>16</x:v>
@@ -1306,40 +1303,43 @@
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="B33" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="J33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="B34" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="B35" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="B36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>88</x:v>
@@ -1348,113 +1348,104 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
+      <x:c r="A37" s="1">
+        <x:v>45061</x:v>
+      </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="1">
-        <x:v>45061</x:v>
+        <x:v>45055</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
-      <x:c r="A39" s="1">
-        <x:v>45055</x:v>
-      </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E39" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="I39" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="B40" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="J40" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="B41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="B42" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="B43" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="B44" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
@@ -1462,62 +1453,54 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="B46" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:11">
+      <x:c r="A47" s="1">
+        <x:v>45014</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-    </x:row>
-    <x:row r="47" spans="1:11">
-      <x:c r="B47" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>112</x:v>
+      <x:c r="E47" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>117</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
-      <x:c r="A48" s="1">
-        <x:v>45014</x:v>
-      </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H48" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:11">
-      <x:c r="B49" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G49" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="J49" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>qHaJ7</x:t>
+    <x:t>pae4l</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -67,43 +67,37 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>PC-9F3D-XY42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz101</x:t>
+    <x:t>PC-D1C0-C08S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rahlyayaa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0300000000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC staus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raa22344erf1@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>125412</x:t>
+  </x:si>
+  <x:si>
+    <x:t>move to client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raamamama3441@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawaz5</x:t>
   </x:si>
   <x:si>
     <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0300000000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QC staus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>125412</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rahlyayaa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raa22344erf1@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>move to client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raamamama3441@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mawaz5</x:t>
   </x:si>
   <x:si>
     <x:t>mawaz6984@mail.com</x:t>
@@ -447,8 +441,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K48" totalsRowShown="0">
-  <x:autoFilter ref="A1:K48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K47" totalsRowShown="0">
+  <x:autoFilter ref="A1:K47"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="First Name"/>
@@ -754,7 +748,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K48"/>
+  <x:dimension ref="A1:K47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -840,19 +834,19 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="B4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>23</x:v>
@@ -863,16 +857,13 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="B5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>28</x:v>
@@ -889,7 +880,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>20</x:v>
@@ -909,7 +900,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>20</x:v>
@@ -929,7 +920,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>20</x:v>
@@ -949,7 +940,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>20</x:v>
@@ -966,7 +957,7 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="B10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>19</x:v>
@@ -975,7 +966,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>23</x:v>
@@ -986,16 +977,16 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="B11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>23</x:v>
@@ -1006,16 +997,16 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="B12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>23</x:v>
@@ -1026,16 +1017,16 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="B13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>23</x:v>
@@ -1046,10 +1037,10 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="B14" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>20</x:v>
@@ -1066,16 +1057,19 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="B15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
         <x:v>23</x:v>
@@ -1086,53 +1080,41 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="B16" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I16" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="B17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="B18" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="I18" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
         <x:v>16</x:v>
@@ -1140,10 +1122,10 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="B19" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
         <x:v>16</x:v>
@@ -1208,8 +1190,11 @@
       <x:c r="B25" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>16</x:v>
@@ -1217,35 +1202,35 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="B26" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="B27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="B28" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
         <x:v>16</x:v>
@@ -1253,9 +1238,6 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="B29" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
@@ -1280,8 +1262,11 @@
       <x:c r="B31" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
         <x:v>16</x:v>
@@ -1291,112 +1276,106 @@
       <x:c r="B32" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D32" s="0" t="s">
+      <x:c r="G32" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="B33" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="B34" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="B35" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
+      <x:c r="G35" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="I35" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
+      <x:c r="A36" s="1">
+        <x:v>45061</x:v>
+      </x:c>
       <x:c r="B36" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="I36" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1">
-        <x:v>45061</x:v>
+        <x:v>45055</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
-      <x:c r="A38" s="1">
-        <x:v>45055</x:v>
-      </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E38" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G38" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H38" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="I38" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
@@ -1407,7 +1386,7 @@
       <x:c r="B39" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="J39" s="0" t="s">
+      <x:c r="D39" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
     </x:row>
@@ -1421,87 +1400,79 @@
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="B41" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="B42" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="B43" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="B44" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="B45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
+      <x:c r="A46" s="1">
+        <x:v>45014</x:v>
+      </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
-      <x:c r="A47" s="1">
-        <x:v>45014</x:v>
-      </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E47" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H47" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:11">
-      <x:c r="B48" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G48" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="J48" s="0" t="s">
-        <x:v>120</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>pae4l</x:t>
+    <x:t>Luo9C</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -67,7 +67,7 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>PC-D1C0-C08S</x:t>
+    <x:t>PC-E3B3-G21M</x:t>
   </x:si>
   <x:si>
     <x:t>rahlyayaa</x:t>
@@ -80,9 +80,6 @@
   </x:si>
   <x:si>
     <x:t>QC staus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raa22344erf1@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>125412</x:t>
@@ -822,14 +819,8 @@
       <x:c r="F3" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="I3" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -843,13 +834,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
         <x:v>16</x:v>
@@ -857,19 +848,19 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="B5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
         <x:v>16</x:v>
@@ -877,19 +868,19 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="B6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
         <x:v>16</x:v>
@@ -897,19 +888,19 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="B7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>16</x:v>
@@ -917,19 +908,19 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="B8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>16</x:v>
@@ -937,19 +928,19 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="B9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
         <x:v>16</x:v>
@@ -966,10 +957,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>16</x:v>
@@ -986,10 +977,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
         <x:v>16</x:v>
@@ -1006,10 +997,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
         <x:v>16</x:v>
@@ -1026,10 +1017,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
         <x:v>16</x:v>
@@ -1037,7 +1028,7 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="B14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>19</x:v>
@@ -1046,10 +1037,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
         <x:v>16</x:v>
@@ -1057,7 +1048,7 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="B15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>19</x:v>
@@ -1069,10 +1060,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
         <x:v>16</x:v>
@@ -1080,30 +1071,30 @@
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="B16" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G16" s="0" t="s">
+      <x:c r="J16" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="J16" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="B17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
         <x:v>16</x:v>
@@ -1111,10 +1102,10 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="B18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
         <x:v>16</x:v>
@@ -1122,10 +1113,10 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="B19" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
         <x:v>16</x:v>
@@ -1133,10 +1124,10 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="B20" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>16</x:v>
@@ -1144,10 +1135,10 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="B21" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>16</x:v>
@@ -1155,10 +1146,10 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="B22" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>16</x:v>
@@ -1166,10 +1157,10 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="B23" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>16</x:v>
@@ -1177,10 +1168,10 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="B24" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
         <x:v>16</x:v>
@@ -1188,13 +1179,13 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="B25" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D25" s="0" t="s">
+      <x:c r="G25" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
         <x:v>16</x:v>
@@ -1202,21 +1193,21 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="B26" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G26" s="0" t="s">
+      <x:c r="J26" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="B27" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
         <x:v>16</x:v>
@@ -1224,13 +1215,13 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="B28" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D28" s="0" t="s">
+      <x:c r="G28" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
         <x:v>16</x:v>
@@ -1238,10 +1229,10 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="B29" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
         <x:v>16</x:v>
@@ -1249,10 +1240,10 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="B30" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="G30" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
         <x:v>16</x:v>
@@ -1260,13 +1251,13 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="B31" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
         <x:v>16</x:v>
@@ -1274,55 +1265,55 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="B32" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="G32" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="B33" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D33" s="0" t="s">
+      <x:c r="G33" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="G33" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="B34" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D34" s="0" t="s">
+      <x:c r="E34" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E34" s="0" t="s">
+      <x:c r="G34" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G34" s="0" t="s">
+      <x:c r="I34" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="B35" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G35" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -1330,19 +1321,19 @@
         <x:v>45061</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="E36" s="0" t="s">
+      <x:c r="G36" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G36" s="0" t="s">
+      <x:c r="H36" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="H36" s="0" t="s">
-        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
@@ -1350,92 +1341,92 @@
         <x:v>45055</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="H37" s="0" t="s">
+      <x:c r="I37" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="I37" s="0" t="s">
+      <x:c r="J37" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="J37" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="B38" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="J38" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="B39" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="B40" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="B41" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="B42" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="B43" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="B44" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="B45" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="D45" s="0" t="s">
+      <x:c r="J45" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -1443,19 +1434,19 @@
         <x:v>45014</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
+      <x:c r="G46" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G46" s="0" t="s">
+      <x:c r="H46" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="H46" s="0" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
         <x:v>16</x:v>
@@ -1463,16 +1454,16 @@
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="B47" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G47" s="0" t="s">
+      <x:c r="J47" s="0" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="J47" s="0" t="s">
-        <x:v>118</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/PotentialClientsList.xlsx
+++ b/cypress/downloads/PotentialClientsList.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <x:si>
     <x:t>ContactDate</x:t>
   </x:si>
@@ -52,7 +52,7 @@
     <x:t>test potential client</x:t>
   </x:si>
   <x:si>
-    <x:t>Luo9C</x:t>
+    <x:t>TCnR5</x:t>
   </x:si>
   <x:si>
     <x:t>211267313</x:t>
@@ -67,7 +67,16 @@
     <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>PC-E3B3-G21M</x:t>
+    <x:t>PC-EC22-VOV9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jason client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PC-CEC0-2A7A</x:t>
   </x:si>
   <x:si>
     <x:t>rahlyayaa</x:t>
@@ -438,8 +447,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K47" totalsRowShown="0">
-  <x:autoFilter ref="A1:K47"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:K48" totalsRowShown="0">
+  <x:autoFilter ref="A1:K48"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="ContactDate"/>
     <x:tableColumn id="2" name="First Name"/>
@@ -745,7 +754,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K47"/>
+  <x:dimension ref="A1:K48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -813,54 +822,48 @@
       <x:c r="D3" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="B5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
         <x:v>16</x:v>
@@ -871,16 +874,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
         <x:v>16</x:v>
@@ -888,19 +891,19 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="B7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
         <x:v>16</x:v>
@@ -908,19 +911,19 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="B8" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>16</x:v>
@@ -928,19 +931,19 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="B9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
         <x:v>16</x:v>
@@ -948,19 +951,19 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="B10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>16</x:v>
@@ -968,19 +971,19 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="B11" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
         <x:v>16</x:v>
@@ -988,19 +991,19 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="B12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
         <x:v>16</x:v>
@@ -1008,19 +1011,19 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="B13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
         <x:v>16</x:v>
@@ -1028,19 +1031,19 @@
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="B14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
         <x:v>16</x:v>
@@ -1048,22 +1051,19 @@
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
         <x:v>16</x:v>
@@ -1073,39 +1073,51 @@
       <x:c r="B16" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="B17" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D17" s="0" t="s">
+      <x:c r="G17" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
+      <x:c r="J17" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="B18" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
         <x:v>16</x:v>
@@ -1113,10 +1125,10 @@
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="B19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
         <x:v>16</x:v>
@@ -1124,10 +1136,10 @@
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="B20" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
         <x:v>16</x:v>
@@ -1135,10 +1147,10 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="B21" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
         <x:v>16</x:v>
@@ -1146,10 +1158,10 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="B22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
         <x:v>16</x:v>
@@ -1157,10 +1169,10 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="B23" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
         <x:v>16</x:v>
@@ -1168,10 +1180,10 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="B24" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
         <x:v>16</x:v>
@@ -1179,9 +1191,6 @@
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="B25" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
@@ -1195,11 +1204,14 @@
       <x:c r="B26" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -1210,14 +1222,11 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="B28" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
@@ -1231,8 +1240,11 @@
       <x:c r="B29" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
         <x:v>16</x:v>
@@ -1240,10 +1252,10 @@
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="B30" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
         <x:v>16</x:v>
@@ -1251,13 +1263,10 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="B31" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
         <x:v>16</x:v>
@@ -1265,17 +1274,20 @@
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="B32" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="B33" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
@@ -1289,181 +1301,192 @@
       <x:c r="D34" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E34" s="0" t="s">
+      <x:c r="G34" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="G34" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="I34" s="0" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="B35" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E35" s="0" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:11">
+      <x:c r="B36" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-    </x:row>
-    <x:row r="36" spans="1:11">
-      <x:c r="A36" s="1">
-        <x:v>45061</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H36" s="0" t="s">
-        <x:v>94</x:v>
+      <x:c r="I36" s="0" t="s">
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="1">
+        <x:v>45061</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:11">
+      <x:c r="A38" s="1">
         <x:v>45055</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G37" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H37" s="0" t="s">
+      <x:c r="B38" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="I37" s="0" t="s">
+      <x:c r="D38" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="J37" s="0" t="s">
+      <x:c r="F38" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38" spans="1:11">
-      <x:c r="B38" s="0" t="s">
+      <x:c r="H38" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="B39" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
         <x:v>104</x:v>
+      </x:c>
+      <x:c r="J39" s="0" t="s">
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="B40" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="B41" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="B42" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="B43" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="B44" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="B45" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="J45" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
-      <x:c r="A46" s="1">
-        <x:v>45014</x:v>
-      </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G46" s="0" t="s">
+      <x:c r="J46" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H46" s="0" t="s">
+    </x:row>
+    <x:row r="47" spans="1:11">
+      <x:c r="A47" s="1">
+        <x:v>45014</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="J46" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:11">
-      <x:c r="B47" s="0" t="s">
+      <x:c r="D47" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:11">
+      <x:c r="B48" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
